--- a/setpoint-sample-client-pack.xlsx
+++ b/setpoint-sample-client-pack.xlsx
@@ -4177,10 +4177,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.140255390412393"/>
-          <c:y val="0.0517410495340853"/>
-          <c:w val="0.822901402553904"/>
-          <c:h val="0.576262873957823"/>
+          <c:x val="0.140284757118928"/>
+          <c:y val="0.0517664376840039"/>
+          <c:w val="0.822654941373534"/>
+          <c:h val="0.576054955839058"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -4651,11 +4651,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="85988402"/>
-        <c:axId val="63078952"/>
+        <c:axId val="19241484"/>
+        <c:axId val="18049124"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="85988402"/>
+        <c:axId val="19241484"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4685,7 +4685,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63078952"/>
+        <c:crossAx val="18049124"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4693,7 +4693,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="63078952"/>
+        <c:axId val="18049124"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4723,7 +4723,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85988402"/>
+        <c:crossAx val="19241484"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:dispUnits>
@@ -4888,8 +4888,8 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="41859788"/>
-        <c:axId val="20006553"/>
+        <c:axId val="71505357"/>
+        <c:axId val="99982467"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5056,11 +5056,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="66816449"/>
-        <c:axId val="46419458"/>
+        <c:axId val="51529024"/>
+        <c:axId val="36782396"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="41859788"/>
+        <c:axId val="71505357"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5090,7 +5090,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20006553"/>
+        <c:crossAx val="99982467"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5098,7 +5098,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20006553"/>
+        <c:axId val="99982467"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5128,7 +5128,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41859788"/>
+        <c:crossAx val="71505357"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:dispUnits>
@@ -5137,7 +5137,7 @@
         </c:dispUnits>
       </c:valAx>
       <c:catAx>
-        <c:axId val="66816449"/>
+        <c:axId val="51529024"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5169,14 +5169,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46419458"/>
+        <c:crossAx val="36782396"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46419458"/>
+        <c:axId val="36782396"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5206,7 +5206,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66816449"/>
+        <c:crossAx val="51529024"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5269,9 +5269,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1026720</xdr:colOff>
+      <xdr:colOff>1026000</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>398520</xdr:rowOff>
+      <xdr:rowOff>397800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5280,7 +5280,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="84600" y="4969800"/>
-        <a:ext cx="3439080" cy="1467720"/>
+        <a:ext cx="3438360" cy="1467000"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5299,9 +5299,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>74160</xdr:colOff>
+      <xdr:colOff>73440</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>283680</xdr:rowOff>
+      <xdr:rowOff>282960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5310,7 +5310,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3725640" y="4938480"/>
-        <a:ext cx="2963160" cy="1384200"/>
+        <a:ext cx="2962440" cy="1383480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -22552,7 +22552,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFB85C38"/>
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:Q54"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="0"/>
@@ -23530,7 +23530,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/setpoint-sample-client-pack.xlsx
+++ b/setpoint-sample-client-pack.xlsx
@@ -4194,10 +4194,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.140387637506548"/>
-          <c:y val="0.0518682399213373"/>
-          <c:w val="0.821791513881613"/>
-          <c:h val="0.575221238938053"/>
+          <c:x val="0.140402347024308"/>
+          <c:y val="0.0518809933611999"/>
+          <c:w val="0.821668063704946"/>
+          <c:h val="0.575116793705434"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -4682,11 +4682,11 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="19563738"/>
-        <c:axId val="96889971"/>
+        <c:axId val="95566846"/>
+        <c:axId val="33372226"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19563738"/>
+        <c:axId val="95566846"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4716,7 +4716,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96889971"/>
+        <c:crossAx val="33372226"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4724,7 +4724,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="96889971"/>
+        <c:axId val="33372226"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4754,7 +4754,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19563738"/>
+        <c:crossAx val="95566846"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:dispUnits>
@@ -4993,8 +4993,8 @@
         </c:ser>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="74439238"/>
-        <c:axId val="55787054"/>
+        <c:axId val="54320314"/>
+        <c:axId val="31913544"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -5161,11 +5161,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="66902886"/>
-        <c:axId val="67084569"/>
+        <c:axId val="1427892"/>
+        <c:axId val="45297032"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="74439238"/>
+        <c:axId val="54320314"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5195,7 +5195,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55787054"/>
+        <c:crossAx val="31913544"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5203,7 +5203,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55787054"/>
+        <c:axId val="31913544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5233,7 +5233,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74439238"/>
+        <c:crossAx val="54320314"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:dispUnits>
@@ -5242,7 +5242,7 @@
         </c:dispUnits>
       </c:valAx>
       <c:catAx>
-        <c:axId val="66902886"/>
+        <c:axId val="1427892"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5274,14 +5274,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67084569"/>
+        <c:crossAx val="45297032"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67084569"/>
+        <c:axId val="45297032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5311,7 +5311,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66902886"/>
+        <c:crossAx val="1427892"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5378,9 +5378,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1023480</xdr:colOff>
+      <xdr:colOff>1023120</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>395280</xdr:rowOff>
+      <xdr:rowOff>394920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5389,7 +5389,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="84600" y="6579720"/>
-        <a:ext cx="3435840" cy="1464120"/>
+        <a:ext cx="3435480" cy="1463760"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5408,9 +5408,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>258480</xdr:colOff>
+      <xdr:colOff>258120</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>280440</xdr:rowOff>
+      <xdr:rowOff>280080</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -5419,7 +5419,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="3725640" y="6548400"/>
-        <a:ext cx="3147480" cy="1380600"/>
+        <a:ext cx="3147120" cy="1380240"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -14477,7 +14477,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:J62"/>
   <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
